--- a/artfynd/A 17210-2026 artfynd.xlsx
+++ b/artfynd/A 17210-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129315516</v>
       </c>
       <c r="B2" t="n">
-        <v>58106</v>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129314844</v>
+        <v>129315541</v>
       </c>
       <c r="B3" t="n">
-        <v>98691</v>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,31 +806,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,13 +839,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608826</v>
+        <v>608938</v>
       </c>
       <c r="R3" t="n">
-        <v>6778152</v>
+        <v>6778160</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,22 +869,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Adam Moore</t>
+          <t>Indre Cepukaite</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129314850</v>
+        <v>129315962</v>
       </c>
       <c r="B4" t="n">
-        <v>98691</v>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,31 +926,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608884</v>
+        <v>608881</v>
       </c>
       <c r="R4" t="n">
-        <v>6778093</v>
+        <v>6778188</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,22 +989,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Adam Moore</t>
+          <t>Indre Cepukaite</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129314847</v>
+        <v>129315967</v>
       </c>
       <c r="B5" t="n">
-        <v>98691</v>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,31 +1046,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1079,13 +1079,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608887</v>
+        <v>608871</v>
       </c>
       <c r="R5" t="n">
-        <v>6778150</v>
+        <v>6778092</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Adam Moore</t>
+          <t>Indre Cepukaite</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1155,32 +1155,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129314843</v>
+        <v>129315971</v>
       </c>
       <c r="B6" t="n">
-        <v>98691</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1188,9 +1188,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1199,13 +1199,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>608800</v>
+        <v>608776</v>
       </c>
       <c r="R6" t="n">
-        <v>6778143</v>
+        <v>6778130</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,22 +1229,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Adam Moore</t>
+          <t>Indre Cepukaite</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1275,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129314845</v>
+        <v>129315526</v>
       </c>
       <c r="B7" t="n">
-        <v>98691</v>
+        <v>58636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,31 +1286,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>103044</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>608846</v>
+        <v>608928</v>
       </c>
       <c r="R7" t="n">
-        <v>6778129</v>
+        <v>6778155</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1349,22 +1349,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,10 +1384,850 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Storgrundet - Klompletering NVI med Fåglar</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129314842</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långsva, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>608786</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6778122</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
           <t>Adam Moore</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Storgrundet - Klompletering NVI med Fåglar</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129314843</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långsva, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>608800</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6778143</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Adam Moore</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Storgrundet - Klompletering NVI med Fåglar</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129314844</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långsva, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>608826</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6778152</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Adam Moore</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Storgrundet - Klompletering NVI med Fåglar</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129314845</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Långsva, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>608846</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6778129</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Adam Moore</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Storgrundet - Klompletering NVI med Fåglar</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129314847</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långsva, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>608887</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6778150</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Adam Moore</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Storgrundet - Klompletering NVI med Fåglar</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129314849</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långsva, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>608916</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6778103</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Adam Moore</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Storgrundet - Klompletering NVI med Fåglar</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129314850</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långsva, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>608884</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6778093</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skog</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Adam Moore</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
         <is>
           <t>Storgrundet - Klompletering NVI med Fåglar</t>
         </is>
